--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20140802</t>
-  </si>
-  <si>
-    <t>IDM TISU DAPUR 1+1</t>
+    <t>20135746</t>
+  </si>
+  <si>
+    <t>MAKUKU AIR DIAPR L26</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -28,120 +28,114 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20012007</t>
+  </si>
+  <si>
+    <t>DAIA DET.BBK PTH 800</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20000980</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET 318ML</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20093100</t>
+  </si>
+  <si>
+    <t>ZEN BW A.BAC SHIS480</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20044351</t>
+  </si>
+  <si>
+    <t>SHINZU'I B/CLN KR480</t>
+  </si>
+  <si>
+    <t>20138649</t>
+  </si>
+  <si>
+    <t>EMRN SHP BT21 AK 340</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20135858</t>
+  </si>
+  <si>
+    <t>F&amp;N EDT OCN SCRET100</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20048310</t>
+  </si>
+  <si>
+    <t>GRNIER ACNO FIGHT 50</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20139602</t>
+  </si>
+  <si>
+    <t>AZZURA DB FC WSH 100</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20139605</t>
+  </si>
+  <si>
+    <t>AZZURA SS SPF 50 30G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20130188</t>
+  </si>
+  <si>
+    <t>HANASUI BRGHT SRM 20</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20074122</t>
+  </si>
+  <si>
+    <t>EMCO HOT SHOTS BOLT</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20135746</t>
-  </si>
-  <si>
-    <t>MAKUKU AIR DIAPR L26</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20012007</t>
-  </si>
-  <si>
-    <t>DAIA DET.BBK PTH 800</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20000980</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET 318ML</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20093100</t>
-  </si>
-  <si>
-    <t>ZEN BW A.BAC SHIS480</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20044351</t>
-  </si>
-  <si>
-    <t>SHINZU'I B/CLN KR480</t>
-  </si>
-  <si>
-    <t>20138649</t>
-  </si>
-  <si>
-    <t>EMRN SHP BT21 AK 340</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20135858</t>
-  </si>
-  <si>
-    <t>F&amp;N EDT OCN SCRET100</t>
-  </si>
-  <si>
-    <t>20048310</t>
-  </si>
-  <si>
-    <t>GRNIER ACNO FIGHT 50</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20139602</t>
-  </si>
-  <si>
-    <t>AZZURA DB FC WSH 100</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20139605</t>
-  </si>
-  <si>
-    <t>AZZURA SS SPF 50 30G</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20130188</t>
-  </si>
-  <si>
-    <t>HANASUI BRGHT SRM 20</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20074122</t>
-  </si>
-  <si>
-    <t>EMCO HOT SHOTS BOLT</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>20076052</t>
   </si>
   <si>
@@ -187,34 +181,40 @@
     <t>PRONAS CORNED BF.198</t>
   </si>
   <si>
-    <t>10003974</t>
-  </si>
-  <si>
-    <t>TROPICAL MNYK BTL 2L</t>
-  </si>
-  <si>
-    <t>20132871</t>
-  </si>
-  <si>
-    <t>DK RONI RS.CORN 135G</t>
-  </si>
-  <si>
-    <t>20097515</t>
-  </si>
-  <si>
-    <t>IDM POP CORN CRML 75</t>
-  </si>
-  <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
-  </si>
-  <si>
-    <t>20139699</t>
-  </si>
-  <si>
-    <t>OASIS  MNRL PH9 500</t>
+    <t>10008989</t>
+  </si>
+  <si>
+    <t>BIMOLI MYK.GRG REF2L</t>
+  </si>
+  <si>
+    <t>10038932</t>
+  </si>
+  <si>
+    <t>KPL API SPC MIX 10'S</t>
+  </si>
+  <si>
+    <t>20027097</t>
+  </si>
+  <si>
+    <t>INDOFOOD SMBL EXT275</t>
+  </si>
+  <si>
+    <t>20025825</t>
+  </si>
+  <si>
+    <t>PRONAS KORNETKU 200G</t>
+  </si>
+  <si>
+    <t>20096677</t>
+  </si>
+  <si>
+    <t>IDM SOES COKELAT 80</t>
+  </si>
+  <si>
+    <t>20136102</t>
+  </si>
+  <si>
+    <t>IDM SOES STROBERI80G</t>
   </si>
   <si>
     <t>20140823</t>
@@ -726,22 +726,22 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
@@ -749,70 +749,70 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -832,7 +832,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -852,7 +852,7 @@
         <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -872,7 +872,7 @@
         <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -892,27 +892,27 @@
         <v>39</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -949,10 +949,10 @@
         <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -969,10 +969,10 @@
         <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -989,18 +989,18 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1012,7 +1012,7 @@
         <v>30</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1032,7 +1032,7 @@
         <v>33</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1046,13 +1046,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1066,13 +1066,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1086,13 +1086,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1106,13 +1106,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1126,13 +1126,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1146,13 +1146,13 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1166,13 +1166,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1186,13 +1186,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1206,13 +1206,13 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="42">
   <si>
     <t/>
   </si>
   <si>
-    <t>20135746</t>
-  </si>
-  <si>
-    <t>MAKUKU AIR DIAPR L26</t>
+    <t>20135747</t>
+  </si>
+  <si>
+    <t>MAKUKU AIR DIAP XL24</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -31,10 +31,22 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20012007</t>
-  </si>
-  <si>
-    <t>DAIA DET.BBK PTH 800</t>
+    <t>20073425</t>
+  </si>
+  <si>
+    <t>IDM P.PRNG JRK.N 650</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20128706</t>
+  </si>
+  <si>
+    <t>ROYALE LNVDR VNL 680</t>
   </si>
   <si>
     <t>2</t>
@@ -43,196 +55,88 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20000980</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET 318ML</t>
+    <t>20093516</t>
+  </si>
+  <si>
+    <t>INDOMARET KUACI 80G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20093100</t>
-  </si>
-  <si>
-    <t>ZEN BW A.BAC SHIS480</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20044351</t>
-  </si>
-  <si>
-    <t>SHINZU'I B/CLN KR480</t>
-  </si>
-  <si>
-    <t>20138649</t>
-  </si>
-  <si>
-    <t>EMRN SHP BT21 AK 340</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20135858</t>
-  </si>
-  <si>
-    <t>F&amp;N EDT OCN SCRET100</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20048310</t>
-  </si>
-  <si>
-    <t>GRNIER ACNO FIGHT 50</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20112944</t>
+  </si>
+  <si>
+    <t>IDM KUACI SUSU 80G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20139602</t>
-  </si>
-  <si>
-    <t>AZZURA DB FC WSH 100</t>
+    <t>20103297</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP200</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20011008</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 400</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20041399</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 400</t>
+  </si>
+  <si>
+    <t>20040217</t>
+  </si>
+  <si>
+    <t>LFBUOY BW C.FRSH 400</t>
+  </si>
+  <si>
+    <t>20011007</t>
+  </si>
+  <si>
+    <t>LFBUOY BW M.CARE 400</t>
+  </si>
+  <si>
+    <t>20067202</t>
+  </si>
+  <si>
+    <t>PONDS PW PR.CHR100G</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20139605</t>
-  </si>
-  <si>
-    <t>AZZURA SS SPF 50 30G</t>
+    <t>20067210</t>
+  </si>
+  <si>
+    <t>PONDS PW NSRCNL 100G</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20130188</t>
-  </si>
-  <si>
-    <t>HANASUI BRGHT SRM 20</t>
+    <t>20136932</t>
+  </si>
+  <si>
+    <t>CTRA LOT BGKOANG 210</t>
   </si>
   <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>20074122</t>
-  </si>
-  <si>
-    <t>EMCO HOT SHOTS BOLT</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20076052</t>
-  </si>
-  <si>
-    <t>PUCUK TEH MLTI 1.3L</t>
-  </si>
-  <si>
-    <t>20019631</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK 1L</t>
-  </si>
-  <si>
-    <t>20122061</t>
-  </si>
-  <si>
-    <t>OATSDE O/M B/BLND 1L</t>
-  </si>
-  <si>
-    <t>20094328</t>
-  </si>
-  <si>
-    <t>PIATTOS SMB GPREK 65</t>
-  </si>
-  <si>
-    <t>20129562</t>
-  </si>
-  <si>
-    <t>IDM FD STRW CHOC 45G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20096796</t>
-  </si>
-  <si>
-    <t>IDM SPREAD CHOC 150</t>
-  </si>
-  <si>
-    <t>10000135</t>
-  </si>
-  <si>
-    <t>PRONAS CORNED BF.198</t>
-  </si>
-  <si>
-    <t>10008989</t>
-  </si>
-  <si>
-    <t>BIMOLI MYK.GRG REF2L</t>
-  </si>
-  <si>
-    <t>10038932</t>
-  </si>
-  <si>
-    <t>KPL API SPC MIX 10'S</t>
-  </si>
-  <si>
-    <t>20027097</t>
-  </si>
-  <si>
-    <t>INDOFOOD SMBL EXT275</t>
-  </si>
-  <si>
-    <t>20025825</t>
-  </si>
-  <si>
-    <t>PRONAS KORNETKU 200G</t>
-  </si>
-  <si>
-    <t>20096677</t>
-  </si>
-  <si>
-    <t>IDM SOES COKELAT 80</t>
-  </si>
-  <si>
-    <t>20136102</t>
-  </si>
-  <si>
-    <t>IDM SOES STROBERI80G</t>
-  </si>
-  <si>
-    <t>20140823</t>
-  </si>
-  <si>
-    <t>IDM PIRING OPAL 26.5</t>
-  </si>
-  <si>
-    <t>20140822</t>
-  </si>
-  <si>
-    <t>IDM PIRING OPAL 21.5</t>
-  </si>
-  <si>
-    <t>20140820</t>
-  </si>
-  <si>
-    <t>IDM MNGKOK OPAL 17.5</t>
   </si>
 </sst>
 </file>
@@ -625,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -706,10 +610,10 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>13</v>
@@ -726,41 +630,41 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -769,18 +673,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -789,38 +693,38 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -829,10 +733,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -849,370 +753,70 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="86">
   <si>
     <t/>
   </si>
@@ -31,6 +31,30 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
+    <t>20069547</t>
+  </si>
+  <si>
+    <t>IDM DIAPER ADULT 7L</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10034652</t>
+  </si>
+  <si>
+    <t>GLADE OCEAN ESCP 350</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
     <t>20073425</t>
   </si>
   <si>
@@ -46,24 +70,108 @@
     <t>20128706</t>
   </si>
   <si>
-    <t>ROYALE LNVDR VNL 680</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>ROYALE LNVDR VNL 600</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
+    <t>20120995</t>
+  </si>
+  <si>
+    <t>BIORE BF RELAX 725</t>
+  </si>
+  <si>
+    <t>20093100</t>
+  </si>
+  <si>
+    <t>ZEN BW A.BAC SHIS480</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20044351</t>
+  </si>
+  <si>
+    <t>SHINZU'I B/CLN KR480</t>
+  </si>
+  <si>
+    <t>20072006</t>
+  </si>
+  <si>
+    <t>MY BABY TLN PLS LP90</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20078241</t>
+  </si>
+  <si>
+    <t>SOFFELL LOT.APEL 60G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>10028501</t>
+  </si>
+  <si>
+    <t>LACTACYD FEM.HYGN.60</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20137411</t>
+  </si>
+  <si>
+    <t>SHINZUI SRM BRGHT 20</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20133672</t>
+  </si>
+  <si>
+    <t>HNSUI COL.SUNS.SPF50</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20019631</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK 1L</t>
+  </si>
+  <si>
+    <t>20137584</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHOCIP35</t>
+  </si>
+  <si>
+    <t>20137583</t>
+  </si>
+  <si>
+    <t>IDM BROWNIS CHEESE35</t>
+  </si>
+  <si>
     <t>20093516</t>
   </si>
   <si>
     <t>INDOMARET KUACI 80G</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
@@ -73,7 +181,16 @@
     <t>IDM KUACI SUSU 80G</t>
   </si>
   <si>
-    <t>5</t>
+    <t>20113338</t>
+  </si>
+  <si>
+    <t>EMINA CHSE MILD 160G</t>
+  </si>
+  <si>
+    <t>20140013</t>
+  </si>
+  <si>
+    <t>M&amp;M'S CHOC CRSPY 30G</t>
   </si>
   <si>
     <t>20103297</t>
@@ -118,25 +235,40 @@
     <t>PONDS PW PR.CHR100G</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>20067210</t>
   </si>
   <si>
     <t>PONDS PW NSRCNL 100G</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>20136932</t>
   </si>
   <si>
     <t>CTRA LOT BGKOANG 210</t>
   </si>
   <si>
-    <t>8</t>
+    <t>20140823</t>
+  </si>
+  <si>
+    <t>IDM PIRING OPAL 26.5</t>
+  </si>
+  <si>
+    <t>20140822</t>
+  </si>
+  <si>
+    <t>IDM PIRING OPAL 21.5</t>
+  </si>
+  <si>
+    <t>20140820</t>
+  </si>
+  <si>
+    <t>IDM MNGKOK OPAL 17.5</t>
+  </si>
+  <si>
+    <t>20141306</t>
+  </si>
+  <si>
+    <t>IDM COSMETIC HADIAH</t>
   </si>
 </sst>
 </file>
@@ -529,14 +661,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -610,10 +742,10 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>13</v>
@@ -630,10 +762,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>17</v>
@@ -650,13 +782,13 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -673,18 +805,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -696,15 +828,15 @@
         <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -716,15 +848,15 @@
         <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -733,10 +865,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -753,18 +885,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -773,18 +905,18 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -793,18 +925,18 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -813,10 +945,390 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>26</v>
+      <c r="F29" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="79">
   <si>
     <t/>
   </si>
@@ -193,58 +193,37 @@
     <t>M&amp;M'S CHOC CRSPY 30G</t>
   </si>
   <si>
-    <t>20103297</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP200</t>
+    <t>20133704</t>
+  </si>
+  <si>
+    <t>IDM BB.FCL TISSU 70S</t>
   </si>
   <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20011008</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 400</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20041399</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 400</t>
-  </si>
-  <si>
-    <t>20040217</t>
-  </si>
-  <si>
-    <t>LFBUOY BW C.FRSH 400</t>
-  </si>
-  <si>
-    <t>20011007</t>
-  </si>
-  <si>
-    <t>LFBUOY BW M.CARE 400</t>
-  </si>
-  <si>
-    <t>20067202</t>
-  </si>
-  <si>
-    <t>PONDS PW PR.CHR100G</t>
-  </si>
-  <si>
-    <t>20067210</t>
-  </si>
-  <si>
-    <t>PONDS PW NSRCNL 100G</t>
-  </si>
-  <si>
-    <t>20136932</t>
-  </si>
-  <si>
-    <t>CTRA LOT BGKOANG 210</t>
+    <t>20131377</t>
+  </si>
+  <si>
+    <t>KPL API ONE+GULA 10S</t>
+  </si>
+  <si>
+    <t>20138571</t>
+  </si>
+  <si>
+    <t>G/DAY LATTE ORI 10S</t>
+  </si>
+  <si>
+    <t>20040341</t>
+  </si>
+  <si>
+    <t>FITBAR FRTS RSBRY 20</t>
+  </si>
+  <si>
+    <t>20137884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHUPA JELLY FUN MIX </t>
   </si>
   <si>
     <t>20140823</t>
@@ -661,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1128,15 +1107,15 @@
         <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1148,15 +1127,15 @@
         <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1168,15 +1147,15 @@
         <v>16</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1188,75 +1167,75 @@
         <v>30</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1265,69 +1244,9 @@
         <v>30</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" s="1" t="s">
         <v>62</v>
       </c>
     </row>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="64">
   <si>
     <t/>
   </si>
   <si>
-    <t>20135747</t>
-  </si>
-  <si>
-    <t>MAKUKU AIR DIAP XL24</t>
+    <t>20108418</t>
+  </si>
+  <si>
+    <t>SOKLIN PWG HJB GR780</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -28,202 +28,157 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10005803</t>
+  </si>
+  <si>
+    <t>SOKLIN PWNGI RED 780</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20020226</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI PINK 765</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20020245</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI BLUE 765</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10004612</t>
+  </si>
+  <si>
+    <t>SOS P.LNT ORANGE 700</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10004610</t>
+  </si>
+  <si>
+    <t>SOS P/LT APLL REF700</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20069547</t>
-  </si>
-  <si>
-    <t>IDM DIAPER ADULT 7L</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10034652</t>
-  </si>
-  <si>
-    <t>GLADE OCEAN ESCP 350</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>20114021</t>
+  </si>
+  <si>
+    <t>IDM TISU WJH PRM 100</t>
+  </si>
+  <si>
+    <t>20000071</t>
+  </si>
+  <si>
+    <t>INDOMARET FAC.COTTON</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20027997</t>
+  </si>
+  <si>
+    <t>IDM KAMPER NAPTLN150</t>
+  </si>
+  <si>
+    <t>20137582</t>
+  </si>
+  <si>
+    <t>IDM PWNG ROM.AURA720</t>
+  </si>
+  <si>
+    <t>20001402</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI APL 800</t>
+  </si>
+  <si>
+    <t>20131516</t>
+  </si>
+  <si>
+    <t>LARIST DET.FRS BT450</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20130709</t>
+  </si>
+  <si>
+    <t>LUX BW MGC ORCHD 825</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10005473</t>
+  </si>
+  <si>
+    <t>KIT WASH&amp;GLOW PCH720</t>
   </si>
   <si>
     <t>RT</t>
   </si>
   <si>
-    <t>20073425</t>
-  </si>
-  <si>
-    <t>IDM P.PRNG JRK.N 650</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20128706</t>
-  </si>
-  <si>
-    <t>ROYALE LNVDR VNL 600</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20120995</t>
-  </si>
-  <si>
-    <t>BIORE BF RELAX 725</t>
-  </si>
-  <si>
-    <t>20093100</t>
-  </si>
-  <si>
-    <t>ZEN BW A.BAC SHIS480</t>
+    <t>20140679</t>
+  </si>
+  <si>
+    <t>IDM FC.TISSUE 3X80'S</t>
+  </si>
+  <si>
+    <t>20077499</t>
+  </si>
+  <si>
+    <t>PRISTINE 8.6+ BTL600</t>
+  </si>
+  <si>
+    <t>10008882</t>
+  </si>
+  <si>
+    <t>K/API KOPI SPCL 150G</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20044351</t>
-  </si>
-  <si>
-    <t>SHINZU'I B/CLN KR480</t>
-  </si>
-  <si>
-    <t>20072006</t>
-  </si>
-  <si>
-    <t>MY BABY TLN PLS LP90</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20078241</t>
-  </si>
-  <si>
-    <t>SOFFELL LOT.APEL 60G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>10028501</t>
-  </si>
-  <si>
-    <t>LACTACYD FEM.HYGN.60</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20137411</t>
-  </si>
-  <si>
-    <t>SHINZUI SRM BRGHT 20</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20133672</t>
-  </si>
-  <si>
-    <t>HNSUI COL.SUNS.SPF50</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20019631</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK 1L</t>
-  </si>
-  <si>
-    <t>20137584</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHOCIP35</t>
-  </si>
-  <si>
-    <t>20137583</t>
-  </si>
-  <si>
-    <t>IDM BROWNIS CHEESE35</t>
-  </si>
-  <si>
-    <t>20093516</t>
-  </si>
-  <si>
-    <t>INDOMARET KUACI 80G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20112944</t>
-  </si>
-  <si>
-    <t>IDM KUACI SUSU 80G</t>
-  </si>
-  <si>
-    <t>20113338</t>
-  </si>
-  <si>
-    <t>EMINA CHSE MILD 160G</t>
-  </si>
-  <si>
-    <t>20140013</t>
-  </si>
-  <si>
-    <t>M&amp;M'S CHOC CRSPY 30G</t>
-  </si>
-  <si>
-    <t>20133704</t>
-  </si>
-  <si>
-    <t>IDM BB.FCL TISSU 70S</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20131377</t>
-  </si>
-  <si>
-    <t>KPL API ONE+GULA 10S</t>
-  </si>
-  <si>
-    <t>20138571</t>
-  </si>
-  <si>
-    <t>G/DAY LATTE ORI 10S</t>
-  </si>
-  <si>
-    <t>20040341</t>
-  </si>
-  <si>
-    <t>FITBAR FRTS RSBRY 20</t>
-  </si>
-  <si>
-    <t>20137884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHUPA JELLY FUN MIX </t>
+    <t>20136451</t>
+  </si>
+  <si>
+    <t>NSCAFE AMERICANO 10S</t>
+  </si>
+  <si>
+    <t>20136661</t>
+  </si>
+  <si>
+    <t>5 DAYS CHOCO BANANA</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
   </si>
   <si>
     <t>20140823</t>
@@ -640,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -707,15 +662,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -724,18 +679,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -744,58 +699,58 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -804,10 +759,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -824,18 +779,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -844,10 +799,10 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -864,18 +819,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -884,370 +839,250 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
   <si>
     <t/>
   </si>
@@ -118,13 +118,10 @@
     <t>IDM P'LANTAI APL 800</t>
   </si>
   <si>
-    <t>20131516</t>
-  </si>
-  <si>
-    <t>LARIST DET.FRS BT450</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
+    <t>20073425</t>
+  </si>
+  <si>
+    <t>IDM P.PRNG JRK.N 650</t>
   </si>
   <si>
     <t>20130709</t>
@@ -136,40 +133,58 @@
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>10005473</t>
-  </si>
-  <si>
-    <t>KIT WASH&amp;GLOW PCH720</t>
+    <t>20010383</t>
+  </si>
+  <si>
+    <t>LIFEBUOY SHP A/D 340</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20027095</t>
+  </si>
+  <si>
+    <t>MY BABY TELON PLS 60</t>
+  </si>
+  <si>
+    <t>20101463</t>
+  </si>
+  <si>
+    <t>HANNOCHS C/D SNC 5W</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
   <si>
     <t>RT</t>
   </si>
   <si>
-    <t>20140679</t>
-  </si>
-  <si>
-    <t>IDM FC.TISSUE 3X80'S</t>
-  </si>
-  <si>
-    <t>20077499</t>
-  </si>
-  <si>
-    <t>PRISTINE 8.6+ BTL600</t>
-  </si>
-  <si>
-    <t>10008882</t>
-  </si>
-  <si>
-    <t>K/API KOPI SPCL 150G</t>
+    <t>10038932</t>
+  </si>
+  <si>
+    <t>KPL API SPC MIX 10'S</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20136451</t>
-  </si>
-  <si>
-    <t>NSCAFE AMERICANO 10S</t>
+    <t>20060370</t>
+  </si>
+  <si>
+    <t>G/DAY CHOCOCINO 10'S</t>
+  </si>
+  <si>
+    <t>20046081</t>
+  </si>
+  <si>
+    <t>G/D 3IN1 MCCINO 10'S</t>
+  </si>
+  <si>
+    <t>20060371</t>
+  </si>
+  <si>
+    <t>G/DAY VNL.LATTE 10'S</t>
   </si>
   <si>
     <t>20136661</t>
@@ -595,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -862,15 +877,15 @@
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -882,15 +897,15 @@
         <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -899,18 +914,18 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -919,38 +934,38 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -959,18 +974,18 @@
         <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -979,18 +994,18 @@
         <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -999,10 +1014,10 @@
         <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1016,13 +1031,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1036,21 +1051,21 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F22" s="1" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1059,7 +1074,7 @@
         <v>18</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>12</v>
@@ -1067,10 +1082,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1079,9 +1094,49 @@
         <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>12</v>
       </c>
     </row>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="55">
   <si>
     <t/>
   </si>
   <si>
-    <t>20108418</t>
-  </si>
-  <si>
-    <t>SOKLIN PWG HJB GR780</t>
+    <t>20098520</t>
+  </si>
+  <si>
+    <t>IDM TISSUE PNGST 150</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -28,172 +28,136 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20027167</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP400</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10004337</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR/MN1500</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20138950</t>
+  </si>
+  <si>
+    <t>IDM ABON AYAM 80G</t>
+  </si>
+  <si>
+    <t>20096677</t>
+  </si>
+  <si>
+    <t>IDM SOES COKELAT 80</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10005803</t>
-  </si>
-  <si>
-    <t>SOKLIN PWNGI RED 780</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20020226</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI PINK 765</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20020245</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI BLUE 765</t>
+    <t>20136102</t>
+  </si>
+  <si>
+    <t>IDM SOES STROBERI80G</t>
+  </si>
+  <si>
+    <t>20134354</t>
+  </si>
+  <si>
+    <t>IDM SARI BH NANAS220</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10004612</t>
-  </si>
-  <si>
-    <t>SOS P.LNT ORANGE 700</t>
+    <t>20134353</t>
+  </si>
+  <si>
+    <t>IDM S/B NNS&amp;MRKSA220</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10004610</t>
-  </si>
-  <si>
-    <t>SOS P/LT APLL REF700</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>20114021</t>
+  </si>
+  <si>
+    <t>IDM TISU WJH PRM 100</t>
+  </si>
+  <si>
+    <t>20132871</t>
+  </si>
+  <si>
+    <t>DK RONI RS.CORN 135G</t>
+  </si>
+  <si>
+    <t>10015954</t>
+  </si>
+  <si>
+    <t>GAGA 100 JALAPENO 75</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20114021</t>
-  </si>
-  <si>
-    <t>IDM TISU WJH PRM 100</t>
-  </si>
-  <si>
-    <t>20000071</t>
-  </si>
-  <si>
-    <t>INDOMARET FAC.COTTON</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20027997</t>
-  </si>
-  <si>
-    <t>IDM KAMPER NAPTLN150</t>
-  </si>
-  <si>
-    <t>20137582</t>
-  </si>
-  <si>
-    <t>IDM PWNG ROM.AURA720</t>
-  </si>
-  <si>
-    <t>20001402</t>
-  </si>
-  <si>
-    <t>IDM P'LANTAI APL 800</t>
-  </si>
-  <si>
-    <t>20073425</t>
-  </si>
-  <si>
-    <t>IDM P.PRNG JRK.N 650</t>
-  </si>
-  <si>
-    <t>20130709</t>
-  </si>
-  <si>
-    <t>LUX BW MGC ORCHD 825</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20010383</t>
-  </si>
-  <si>
-    <t>LIFEBUOY SHP A/D 340</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20027095</t>
-  </si>
-  <si>
-    <t>MY BABY TELON PLS 60</t>
-  </si>
-  <si>
-    <t>20101463</t>
-  </si>
-  <si>
-    <t>HANNOCHS C/D SNC 5W</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>10038932</t>
-  </si>
-  <si>
-    <t>KPL API SPC MIX 10'S</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20060370</t>
-  </si>
-  <si>
-    <t>G/DAY CHOCOCINO 10'S</t>
-  </si>
-  <si>
-    <t>20046081</t>
-  </si>
-  <si>
-    <t>G/D 3IN1 MCCINO 10'S</t>
-  </si>
-  <si>
-    <t>20060371</t>
-  </si>
-  <si>
-    <t>G/DAY VNL.LATTE 10'S</t>
-  </si>
-  <si>
-    <t>20136661</t>
-  </si>
-  <si>
-    <t>5 DAYS CHOCO BANANA</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
+    <t>20085444</t>
+  </si>
+  <si>
+    <t>GAGA 100 GR.JLPNO 85</t>
+  </si>
+  <si>
+    <t>20054589</t>
+  </si>
+  <si>
+    <t>3SAPI KRIMER 490G</t>
+  </si>
+  <si>
+    <t>20003902</t>
+  </si>
+  <si>
+    <t>KRAFT CHEDDAR 150G</t>
+  </si>
+  <si>
+    <t>20033450</t>
+  </si>
+  <si>
+    <t>QTELA KRP/TMPE ORI55</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20045104</t>
+  </si>
+  <si>
+    <t>QTELA TEMPE CABE/R55</t>
+  </si>
+  <si>
+    <t>20137761</t>
+  </si>
+  <si>
+    <t>LARISST CRISPY CHO50</t>
+  </si>
+  <si>
+    <t>20141306</t>
+  </si>
+  <si>
+    <t>IDM COSMETIC HADIAH</t>
   </si>
   <si>
     <t>20140823</t>
@@ -212,12 +176,6 @@
   </si>
   <si>
     <t>IDM MNGKOK OPAL 17.5</t>
-  </si>
-  <si>
-    <t>20141306</t>
-  </si>
-  <si>
-    <t>IDM COSMETIC HADIAH</t>
   </si>
 </sst>
 </file>
@@ -610,14 +568,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -677,15 +635,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -694,30 +652,30 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -731,41 +689,41 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -774,18 +732,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -794,350 +752,270 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="65">
   <si>
     <t/>
   </si>
@@ -94,88 +94,118 @@
     <t>5</t>
   </si>
   <si>
-    <t>20114021</t>
-  </si>
-  <si>
-    <t>IDM TISU WJH PRM 100</t>
-  </si>
-  <si>
-    <t>20132871</t>
-  </si>
-  <si>
-    <t>DK RONI RS.CORN 135G</t>
-  </si>
-  <si>
-    <t>10015954</t>
-  </si>
-  <si>
-    <t>GAGA 100 JALAPENO 75</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20085444</t>
-  </si>
-  <si>
-    <t>GAGA 100 GR.JLPNO 85</t>
-  </si>
-  <si>
-    <t>20054589</t>
-  </si>
-  <si>
-    <t>3SAPI KRIMER 490G</t>
-  </si>
-  <si>
-    <t>20003902</t>
-  </si>
-  <si>
-    <t>KRAFT CHEDDAR 150G</t>
-  </si>
-  <si>
-    <t>20033450</t>
-  </si>
-  <si>
-    <t>QTELA KRP/TMPE ORI55</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20045104</t>
-  </si>
-  <si>
-    <t>QTELA TEMPE CABE/R55</t>
-  </si>
-  <si>
-    <t>20137761</t>
-  </si>
-  <si>
-    <t>LARISST CRISPY CHO50</t>
+    <t>10003873</t>
+  </si>
+  <si>
+    <t>K/API KOPI BUBUK 350</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20140181</t>
+  </si>
+  <si>
+    <t>KAPAL API SPCL 250G</t>
+  </si>
+  <si>
+    <t>10000102</t>
+  </si>
+  <si>
+    <t>BOTAN MACKEREL 425G</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20134970</t>
+  </si>
+  <si>
+    <t>MILO SANDW ORIG 104G</t>
+  </si>
+  <si>
+    <t>20124346</t>
+  </si>
+  <si>
+    <t>BAYGON JPNSE&amp;PCH 600</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20098605</t>
+  </si>
+  <si>
+    <t>BYGON SPRY CHR.BL600</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20067210</t>
+  </si>
+  <si>
+    <t>PONDS PW NSRCNL 100G</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20067202</t>
+  </si>
+  <si>
+    <t>PONDS PW PR.CHR100G</t>
+  </si>
+  <si>
+    <t>20056356</t>
+  </si>
+  <si>
+    <t>SHNZUI FW LIGHT 80ML</t>
+  </si>
+  <si>
+    <t>RT,(E-9B)</t>
+  </si>
+  <si>
+    <t>20079010</t>
+  </si>
+  <si>
+    <t>SHNZUI F.WASH TUB 80</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10000425</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH 60</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20140823</t>
+  </si>
+  <si>
+    <t>IDM PIRING OPAL 26.5</t>
+  </si>
+  <si>
+    <t>20140822</t>
+  </si>
+  <si>
+    <t>IDM PIRING OPAL 21.5</t>
+  </si>
+  <si>
+    <t>20140820</t>
+  </si>
+  <si>
+    <t>IDM MNGKOK OPAL 17.5</t>
   </si>
   <si>
     <t>20141306</t>
   </si>
   <si>
-    <t>IDM COSMETIC HADIAH</t>
-  </si>
-  <si>
-    <t>20140823</t>
-  </si>
-  <si>
-    <t>IDM PIRING OPAL 26.5</t>
-  </si>
-  <si>
-    <t>20140822</t>
-  </si>
-  <si>
-    <t>IDM PIRING OPAL 21.5</t>
-  </si>
-  <si>
-    <t>20140820</t>
-  </si>
-  <si>
-    <t>IDM MNGKOK OPAL 17.5</t>
+    <t xml:space="preserve">IDM COSMETIC </t>
   </si>
 </sst>
 </file>
@@ -568,14 +598,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -775,15 +805,15 @@
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -800,10 +830,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -815,15 +845,15 @@
         <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -835,15 +865,15 @@
         <v>23</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -855,15 +885,15 @@
         <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -875,15 +905,15 @@
         <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -895,15 +925,15 @@
         <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -915,15 +945,15 @@
         <v>23</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -935,55 +965,55 @@
         <v>26</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -992,7 +1022,7 @@
         <v>26</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1000,10 +1030,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1012,9 +1042,49 @@
         <v>26</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="72">
   <si>
     <t/>
   </si>
   <si>
-    <t>20098520</t>
-  </si>
-  <si>
-    <t>IDM TISSUE PNGST 150</t>
+    <t>20141345</t>
+  </si>
+  <si>
+    <t>LARISST S/PCC PRG650</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -28,166 +28,187 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20001407</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI LAV 800</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20001402</t>
+  </si>
+  <si>
+    <t>IDM P'LANTAI APL 800</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20000071</t>
+  </si>
+  <si>
+    <t>INDOMARET FAC.COTTON</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20052629</t>
+  </si>
+  <si>
+    <t>IDM AIR DGN OKSGN600</t>
+  </si>
+  <si>
+    <t>PT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20093516</t>
+  </si>
+  <si>
+    <t>INDOMARET KUACI 80G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20112944</t>
+  </si>
+  <si>
+    <t>IDM KUACI SUSU 80G</t>
+  </si>
+  <si>
+    <t>20052766</t>
+  </si>
+  <si>
+    <t>IDM KCNG METE MDU 80</t>
+  </si>
+  <si>
+    <t>20126521</t>
+  </si>
+  <si>
+    <t>IDM KCNG METE PDS 70</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20115332</t>
+  </si>
+  <si>
+    <t>IDM SNTAN KELAPA 200</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20038777</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 900ML</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20138599</t>
+  </si>
+  <si>
+    <t>JETZ TOR JG.BKR 140G</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20140272</t>
+  </si>
+  <si>
+    <t>CHIKI TWIST CORN 120</t>
+  </si>
+  <si>
+    <t>RT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20138271</t>
+  </si>
+  <si>
+    <t>N/SHIM STR CHESE 136</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20141816</t>
+  </si>
+  <si>
+    <t>N/SHIM TOOMBA 137GR</t>
+  </si>
+  <si>
+    <t>20140018</t>
+  </si>
+  <si>
+    <t>IDM BB.WIPE RM 2X50S</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20082206</t>
+  </si>
+  <si>
+    <t>SERASOFT SHP DT 170</t>
+  </si>
+  <si>
+    <t>20082205</t>
+  </si>
+  <si>
+    <t>SERASOFT SHP HFT 170</t>
+  </si>
+  <si>
+    <t>20135632</t>
+  </si>
+  <si>
+    <t>SERASOFT SHP SMTH170</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20021816</t>
+  </si>
+  <si>
+    <t>VSLNE LOT BRIGHT 200</t>
+  </si>
+  <si>
+    <t>20126525</t>
+  </si>
+  <si>
+    <t>G&amp;L ULTMTE UV VT.C20</t>
+  </si>
+  <si>
+    <t>20138347</t>
+  </si>
+  <si>
+    <t>G&amp;G SUNSSCREN 15G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20140823</t>
+  </si>
+  <si>
+    <t>IDM PIRING OPAL 26.5</t>
+  </si>
+  <si>
     <t>PT</t>
-  </si>
-  <si>
-    <t>20027167</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP400</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10004337</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR/MN1500</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20138950</t>
-  </si>
-  <si>
-    <t>IDM ABON AYAM 80G</t>
-  </si>
-  <si>
-    <t>20096677</t>
-  </si>
-  <si>
-    <t>IDM SOES COKELAT 80</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20136102</t>
-  </si>
-  <si>
-    <t>IDM SOES STROBERI80G</t>
-  </si>
-  <si>
-    <t>20134354</t>
-  </si>
-  <si>
-    <t>IDM SARI BH NANAS220</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20134353</t>
-  </si>
-  <si>
-    <t>IDM S/B NNS&amp;MRKSA220</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10003873</t>
-  </si>
-  <si>
-    <t>K/API KOPI BUBUK 350</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20140181</t>
-  </si>
-  <si>
-    <t>KAPAL API SPCL 250G</t>
-  </si>
-  <si>
-    <t>10000102</t>
-  </si>
-  <si>
-    <t>BOTAN MACKEREL 425G</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20134970</t>
-  </si>
-  <si>
-    <t>MILO SANDW ORIG 104G</t>
-  </si>
-  <si>
-    <t>20124346</t>
-  </si>
-  <si>
-    <t>BAYGON JPNSE&amp;PCH 600</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20098605</t>
-  </si>
-  <si>
-    <t>BYGON SPRY CHR.BL600</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20067210</t>
-  </si>
-  <si>
-    <t>PONDS PW NSRCNL 100G</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20067202</t>
-  </si>
-  <si>
-    <t>PONDS PW PR.CHR100G</t>
-  </si>
-  <si>
-    <t>20056356</t>
-  </si>
-  <si>
-    <t>SHNZUI FW LIGHT 80ML</t>
-  </si>
-  <si>
-    <t>RT,(E-9B)</t>
-  </si>
-  <si>
-    <t>20079010</t>
-  </si>
-  <si>
-    <t>SHNZUI F.WASH TUB 80</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10000425</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 60</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20140823</t>
-  </si>
-  <si>
-    <t>IDM PIRING OPAL 26.5</t>
   </si>
   <si>
     <t>20140822</t>
@@ -598,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -665,15 +686,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -682,38 +703,38 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -722,18 +743,18 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -742,10 +763,10 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -762,18 +783,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -782,50 +803,50 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -839,10 +860,10 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>34</v>
@@ -859,73 +880,73 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -939,33 +960,33 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -979,93 +1000,93 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1079,13 +1100,73 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
   <si>
     <t/>
   </si>
   <si>
-    <t>20141345</t>
-  </si>
-  <si>
-    <t>LARISST S/PCC PRG650</t>
+    <t>20048847</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP900</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -28,205 +28,196 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20098520</t>
+  </si>
+  <si>
+    <t>IDM TISSUE PNGST 150</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20028779</t>
+  </si>
+  <si>
+    <t>IDM KRBOL WNG650(BR)</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>PT,(E-2B)</t>
   </si>
   <si>
-    <t>20001407</t>
-  </si>
-  <si>
-    <t>IDM P'LANTAI LAV 800</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20001402</t>
-  </si>
-  <si>
-    <t>IDM P'LANTAI APL 800</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20000071</t>
-  </si>
-  <si>
-    <t>INDOMARET FAC.COTTON</t>
+    <t>20089542</t>
+  </si>
+  <si>
+    <t>IDM AIR MN 8+ BTL500</t>
+  </si>
+  <si>
+    <t>RT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20097515</t>
+  </si>
+  <si>
+    <t>IDM POP CORN CRML 75</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20102071</t>
+  </si>
+  <si>
+    <t>IDM POPCRN SW.CHS 65</t>
+  </si>
+  <si>
+    <t>20003915</t>
+  </si>
+  <si>
+    <t>IDM ABON SAPI 100GR</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20052629</t>
-  </si>
-  <si>
-    <t>IDM AIR DGN OKSGN600</t>
-  </si>
-  <si>
-    <t>PT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20093516</t>
-  </si>
-  <si>
-    <t>INDOMARET KUACI 80G</t>
-  </si>
-  <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20112944</t>
-  </si>
-  <si>
-    <t>IDM KUACI SUSU 80G</t>
-  </si>
-  <si>
-    <t>20052766</t>
-  </si>
-  <si>
-    <t>IDM KCNG METE MDU 80</t>
-  </si>
-  <si>
-    <t>20126521</t>
-  </si>
-  <si>
-    <t>IDM KCNG METE PDS 70</t>
+    <t>20071105</t>
+  </si>
+  <si>
+    <t>MITU GP PURPLE 2X50S</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20019170</t>
+  </si>
+  <si>
+    <t>SLEEK CLN BTL NPL450</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20103167</t>
+  </si>
+  <si>
+    <t>MY BABY H&amp;B WSH 375</t>
+  </si>
+  <si>
+    <t>10031470</t>
+  </si>
+  <si>
+    <t>MY BABY PWD S.FLO225</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20133137</t>
+  </si>
+  <si>
+    <t>MY BB FC&amp;BDY CRM 50G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20115332</t>
-  </si>
-  <si>
-    <t>IDM SNTAN KELAPA 200</t>
+    <t>20099248</t>
+  </si>
+  <si>
+    <t>LCTACYD BB.LIQ SP 60</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20038777</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 900ML</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20138599</t>
-  </si>
-  <si>
-    <t>JETZ TOR JG.BKR 140G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20140272</t>
-  </si>
-  <si>
-    <t>CHIKI TWIST CORN 120</t>
-  </si>
-  <si>
-    <t>RT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20138271</t>
-  </si>
-  <si>
-    <t>N/SHIM STR CHESE 136</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20141816</t>
-  </si>
-  <si>
-    <t>N/SHIM TOOMBA 137GR</t>
-  </si>
-  <si>
-    <t>20140018</t>
-  </si>
-  <si>
-    <t>IDM BB.WIPE RM 2X50S</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20082206</t>
-  </si>
-  <si>
-    <t>SERASOFT SHP DT 170</t>
-  </si>
-  <si>
-    <t>20082205</t>
-  </si>
-  <si>
-    <t>SERASOFT SHP HFT 170</t>
-  </si>
-  <si>
-    <t>20135632</t>
-  </si>
-  <si>
-    <t>SERASOFT SHP SMTH170</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20021816</t>
-  </si>
-  <si>
-    <t>VSLNE LOT BRIGHT 200</t>
-  </si>
-  <si>
-    <t>20126525</t>
-  </si>
-  <si>
-    <t>G&amp;L ULTMTE UV VT.C20</t>
-  </si>
-  <si>
-    <t>20138347</t>
-  </si>
-  <si>
-    <t>G&amp;G SUNSSCREN 15G</t>
+    <t>20045887</t>
+  </si>
+  <si>
+    <t>IDM TISU DP/HND 150S</t>
+  </si>
+  <si>
+    <t>20140003</t>
+  </si>
+  <si>
+    <t>RNSO PWD ROSE.F 1.44</t>
+  </si>
+  <si>
+    <t>20139609</t>
+  </si>
+  <si>
+    <t>RNSO JPN PEAC 1440G</t>
+  </si>
+  <si>
+    <t>20093997</t>
+  </si>
+  <si>
+    <t>DIABETAMIL SWTNR 50G</t>
+  </si>
+  <si>
+    <t>10000101</t>
+  </si>
+  <si>
+    <t>BOTAN MACKEREL 155G</t>
+  </si>
+  <si>
+    <t>20102789</t>
+  </si>
+  <si>
+    <t>ABC CHOCMLT COFF 200</t>
+  </si>
+  <si>
+    <t>20102790</t>
+  </si>
+  <si>
+    <t>ABC MILK COFFEE 200</t>
+  </si>
+  <si>
+    <t>10007970</t>
+  </si>
+  <si>
+    <t>BUAVITA JAMBU SL 245</t>
+  </si>
+  <si>
+    <t>10007973</t>
+  </si>
+  <si>
+    <t>BUAVITA MANGGA 245ML</t>
+  </si>
+  <si>
+    <t>10007972</t>
+  </si>
+  <si>
+    <t>BUAVITA JC APPLE 245</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20140823</t>
-  </si>
-  <si>
-    <t>IDM PIRING OPAL 26.5</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20140822</t>
-  </si>
-  <si>
-    <t>IDM PIRING OPAL 21.5</t>
-  </si>
-  <si>
-    <t>20140820</t>
-  </si>
-  <si>
-    <t>IDM MNGKOK OPAL 17.5</t>
+    <t>10007971</t>
+  </si>
+  <si>
+    <t>BUAVITA ORANGE SL245</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>20141306</t>
   </si>
   <si>
     <t xml:space="preserve">IDM COSMETIC </t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
 </sst>
 </file>
@@ -619,14 +610,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -706,35 +697,35 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -743,18 +734,18 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -763,10 +754,10 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -783,78 +774,78 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -863,18 +854,18 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -883,18 +874,18 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -903,30 +894,30 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -940,13 +931,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -960,213 +951,193 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="64">
   <si>
     <t/>
   </si>
@@ -139,85 +139,70 @@
     <t>6</t>
   </si>
   <si>
-    <t>20045887</t>
-  </si>
-  <si>
-    <t>IDM TISU DP/HND 150S</t>
-  </si>
-  <si>
-    <t>20140003</t>
-  </si>
-  <si>
-    <t>RNSO PWD ROSE.F 1.44</t>
-  </si>
-  <si>
-    <t>20139609</t>
-  </si>
-  <si>
-    <t>RNSO JPN PEAC 1440G</t>
-  </si>
-  <si>
-    <t>20093997</t>
-  </si>
-  <si>
-    <t>DIABETAMIL SWTNR 50G</t>
-  </si>
-  <si>
-    <t>10000101</t>
-  </si>
-  <si>
-    <t>BOTAN MACKEREL 155G</t>
-  </si>
-  <si>
-    <t>20102789</t>
-  </si>
-  <si>
-    <t>ABC CHOCMLT COFF 200</t>
-  </si>
-  <si>
-    <t>20102790</t>
-  </si>
-  <si>
-    <t>ABC MILK COFFEE 200</t>
-  </si>
-  <si>
-    <t>10007970</t>
-  </si>
-  <si>
-    <t>BUAVITA JAMBU SL 245</t>
-  </si>
-  <si>
-    <t>10007973</t>
-  </si>
-  <si>
-    <t>BUAVITA MANGGA 245ML</t>
-  </si>
-  <si>
-    <t>10007972</t>
-  </si>
-  <si>
-    <t>BUAVITA JC APPLE 245</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10007971</t>
-  </si>
-  <si>
-    <t>BUAVITA ORANGE SL245</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>20136666</t>
+  </si>
+  <si>
+    <t>LARISST KCG KULIT370</t>
+  </si>
+  <si>
+    <t>20132871</t>
+  </si>
+  <si>
+    <t>DK RONI RS.CORN 135G</t>
+  </si>
+  <si>
+    <t>20112450</t>
+  </si>
+  <si>
+    <t>IDM MEISIS 200G</t>
+  </si>
+  <si>
+    <t>20122061</t>
+  </si>
+  <si>
+    <t>OATSDE O/M B/BLND 1L</t>
+  </si>
+  <si>
+    <t>20140679</t>
+  </si>
+  <si>
+    <t>IDM FC.TISSUE 3X80'S</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20137311</t>
+  </si>
+  <si>
+    <t>MY BBY KD KY PTH 150</t>
+  </si>
+  <si>
+    <t>20126525</t>
+  </si>
+  <si>
+    <t>G&amp;L ULTMTE UV VT.C20</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20138347</t>
+  </si>
+  <si>
+    <t>G&amp;G SUNSSCREN 15G</t>
+  </si>
+  <si>
+    <t>20120995</t>
+  </si>
+  <si>
+    <t>BIORE BF RELAX 725</t>
   </si>
   <si>
     <t>20141306</t>
   </si>
   <si>
     <t xml:space="preserve">IDM COSMETIC </t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
 </sst>
 </file>
@@ -610,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -917,7 +902,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -937,7 +922,7 @@
         <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -957,7 +942,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -971,13 +956,13 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -994,18 +979,18 @@
         <v>38</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1014,18 +999,18 @@
         <v>38</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1034,18 +1019,18 @@
         <v>38</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1054,18 +1039,18 @@
         <v>38</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1074,18 +1059,18 @@
         <v>38</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1094,49 +1079,9 @@
         <v>38</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="55">
   <si>
     <t/>
   </si>
   <si>
-    <t>20048847</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP900</t>
+    <t>20094171</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR 24X200</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -28,181 +28,154 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20114021</t>
+  </si>
+  <si>
+    <t>IDM TISU WJH PRM 100</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20098520</t>
-  </si>
-  <si>
-    <t>IDM TISSUE PNGST 150</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20028779</t>
-  </si>
-  <si>
-    <t>IDM KRBOL WNG650(BR)</t>
+    <t>20140679</t>
+  </si>
+  <si>
+    <t>IDM FC.TISSUE 3X80'S</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20035998</t>
+  </si>
+  <si>
+    <t>INDOMRET TRVL PACK50</t>
+  </si>
+  <si>
+    <t>20133704</t>
+  </si>
+  <si>
+    <t>IDM BB.FCL TISSU 70S</t>
+  </si>
+  <si>
+    <t>20000071</t>
+  </si>
+  <si>
+    <t>INDOMARET FAC.COTTON</t>
+  </si>
+  <si>
     <t>PT,(E-2B)</t>
   </si>
   <si>
-    <t>20089542</t>
-  </si>
-  <si>
-    <t>IDM AIR MN 8+ BTL500</t>
-  </si>
-  <si>
-    <t>RT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20097515</t>
-  </si>
-  <si>
-    <t>IDM POP CORN CRML 75</t>
+    <t>20003915</t>
+  </si>
+  <si>
+    <t>IDM ABON SAPI 100GR</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10029542</t>
+  </si>
+  <si>
+    <t>MR.BREAD COKLAT KEJU</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20102071</t>
-  </si>
-  <si>
-    <t>IDM POPCRN SW.CHS 65</t>
-  </si>
-  <si>
-    <t>20003915</t>
-  </si>
-  <si>
-    <t>IDM ABON SAPI 100GR</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20071105</t>
-  </si>
-  <si>
-    <t>MITU GP PURPLE 2X50S</t>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20019815</t>
+  </si>
+  <si>
+    <t>T/SLM SWT DIAB50X1.8</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10003922</t>
+  </si>
+  <si>
+    <t>ABC KP&amp;GULA+SS.10X30</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20019170</t>
-  </si>
-  <si>
-    <t>SLEEK CLN BTL NPL450</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20103167</t>
-  </si>
-  <si>
-    <t>MY BABY H&amp;B WSH 375</t>
-  </si>
-  <si>
-    <t>10031470</t>
-  </si>
-  <si>
-    <t>MY BABY PWD S.FLO225</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20133137</t>
-  </si>
-  <si>
-    <t>MY BB FC&amp;BDY CRM 50G</t>
+    <t>10000135</t>
+  </si>
+  <si>
+    <t>PRONAS CORNED BF.198</t>
+  </si>
+  <si>
+    <t>20129841</t>
+  </si>
+  <si>
+    <t>IDM MIE GRG PDS 92G</t>
+  </si>
+  <si>
+    <t>20129840</t>
+  </si>
+  <si>
+    <t>IDM MIE GRG INDO 88G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20099248</t>
-  </si>
-  <si>
-    <t>LCTACYD BB.LIQ SP 60</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20136666</t>
-  </si>
-  <si>
-    <t>LARISST KCG KULIT370</t>
-  </si>
-  <si>
-    <t>20132871</t>
-  </si>
-  <si>
-    <t>DK RONI RS.CORN 135G</t>
-  </si>
-  <si>
-    <t>20112450</t>
-  </si>
-  <si>
-    <t>IDM MEISIS 200G</t>
-  </si>
-  <si>
-    <t>20122061</t>
-  </si>
-  <si>
-    <t>OATSDE O/M B/BLND 1L</t>
-  </si>
-  <si>
-    <t>20140679</t>
-  </si>
-  <si>
-    <t>IDM FC.TISSUE 3X80'S</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20137311</t>
-  </si>
-  <si>
-    <t>MY BBY KD KY PTH 150</t>
-  </si>
-  <si>
-    <t>20126525</t>
-  </si>
-  <si>
-    <t>G&amp;L ULTMTE UV VT.C20</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20138347</t>
-  </si>
-  <si>
-    <t>G&amp;G SUNSSCREN 15G</t>
-  </si>
-  <si>
-    <t>20120995</t>
-  </si>
-  <si>
-    <t>BIORE BF RELAX 725</t>
+    <t>20021324</t>
+  </si>
+  <si>
+    <t>LAURIER RLX NG 12/35</t>
+  </si>
+  <si>
+    <t>20056356</t>
+  </si>
+  <si>
+    <t>SHNZUI FW LIGHT 80ML</t>
+  </si>
+  <si>
+    <t>RT,(E-9B)</t>
+  </si>
+  <si>
+    <t>20079010</t>
+  </si>
+  <si>
+    <t>SHNZUI F.WASH TUB 80</t>
   </si>
   <si>
     <t>20141306</t>
   </si>
   <si>
     <t xml:space="preserve">IDM COSMETIC </t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -595,14 +568,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -662,15 +635,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -679,18 +652,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -702,7 +675,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -722,15 +695,15 @@
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -739,10 +712,10 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -762,135 +735,135 @@
         <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -899,18 +872,18 @@
         <v>23</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -919,50 +892,50 @@
         <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -976,113 +949,33 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="55">
   <si>
     <t/>
   </si>
@@ -109,73 +109,73 @@
     <t>PUCUK/H TEH L/SGR350</t>
   </si>
   <si>
-    <t>20019815</t>
-  </si>
-  <si>
-    <t>T/SLM SWT DIAB50X1.8</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10003922</t>
-  </si>
-  <si>
-    <t>ABC KP&amp;GULA+SS.10X30</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10000135</t>
-  </si>
-  <si>
-    <t>PRONAS CORNED BF.198</t>
-  </si>
-  <si>
-    <t>20129841</t>
-  </si>
-  <si>
-    <t>IDM MIE GRG PDS 92G</t>
-  </si>
-  <si>
-    <t>20129840</t>
-  </si>
-  <si>
-    <t>IDM MIE GRG INDO 88G</t>
+    <t>20087202</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 800</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20081452</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 800</t>
+  </si>
+  <si>
+    <t>20084152</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW MLD C800</t>
+  </si>
+  <si>
+    <t>20136390</t>
+  </si>
+  <si>
+    <t>VSLNE LOT DW RDNC100</t>
+  </si>
+  <si>
+    <t>20133375</t>
+  </si>
+  <si>
+    <t>VSLNE LOT FLWLESS100</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20021324</t>
-  </si>
-  <si>
-    <t>LAURIER RLX NG 12/35</t>
-  </si>
-  <si>
-    <t>20056356</t>
-  </si>
-  <si>
-    <t>SHNZUI FW LIGHT 80ML</t>
-  </si>
-  <si>
-    <t>RT,(E-9B)</t>
-  </si>
-  <si>
-    <t>20079010</t>
-  </si>
-  <si>
-    <t>SHNZUI F.WASH TUB 80</t>
-  </si>
-  <si>
-    <t>20141306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDM COSMETIC </t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>20140802</t>
+  </si>
+  <si>
+    <t>IDM TISU DAPUR 1+1</t>
+  </si>
+  <si>
+    <t>20139576</t>
+  </si>
+  <si>
+    <t>PC CRMY CPUCCINO 210</t>
+  </si>
+  <si>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
+  </si>
+  <si>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
+  </si>
+  <si>
+    <t>20141597</t>
+  </si>
+  <si>
+    <t>FRUZZ GUMMY ASORTD36</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
 </sst>
 </file>
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -835,15 +835,15 @@
         <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -855,15 +855,15 @@
         <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -875,15 +875,15 @@
         <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -892,90 +892,110 @@
         <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>9</v>
+      <c r="F21" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="77">
   <si>
     <t/>
   </si>
   <si>
-    <t>20094171</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR 24X200</t>
+    <t>20036197</t>
+  </si>
+  <si>
+    <t>COCA COLA PET 1 LT</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -28,154 +28,220 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20036200</t>
+  </si>
+  <si>
+    <t>SPRITE SOFT DRINK 1L</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20036199</t>
+  </si>
+  <si>
+    <t>FANTA STRAWBERRY 1 L</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20032503</t>
+  </si>
+  <si>
+    <t>MINUTE M. P/ORNGE 1L</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20005529</t>
+  </si>
+  <si>
+    <t>NESTLE PURE LIFE 600</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20090527</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 600mL</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10036647</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU UHT CHO1L</t>
+  </si>
+  <si>
+    <t>10004884</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT CHO 950</t>
+  </si>
+  <si>
+    <t>10005909</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT PLN 950</t>
+  </si>
+  <si>
+    <t>20134390</t>
+  </si>
+  <si>
+    <t>CIMORY BBS LKTSA 250</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20138916</t>
+  </si>
+  <si>
+    <t>CIMORY THAI TEA 250</t>
+  </si>
+  <si>
+    <t>20104636</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CHOML 250</t>
+  </si>
+  <si>
+    <t>20112746</t>
+  </si>
+  <si>
+    <t>INDOMLK KIDS CKLT 6S</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20112794</t>
+  </si>
+  <si>
+    <t>INDOMLK KIDS STRW 6S</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20016512</t>
+  </si>
+  <si>
+    <t>SUNCO MNYK GORENG 2L</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20002725</t>
+  </si>
+  <si>
+    <t>KPL API SPC.MIX 20'S</t>
+  </si>
+  <si>
+    <t>20031318</t>
+  </si>
+  <si>
+    <t>G/DAY CPUCINO 10X25G</t>
+  </si>
+  <si>
+    <t>10002595</t>
+  </si>
+  <si>
+    <t>KRATINGDAENG 150 ML</t>
+  </si>
+  <si>
+    <t>20080924</t>
+  </si>
+  <si>
+    <t>YB BABY CRACK BNN 25</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20141306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDM COSMETIC </t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20135430</t>
+  </si>
+  <si>
+    <t>LAURIER RN 18'S 35CM</t>
+  </si>
+  <si>
+    <t>20140679</t>
+  </si>
+  <si>
+    <t>IDM FC.TISSUE 3X80'S</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20136390</t>
+  </si>
+  <si>
+    <t>VSLNE LOT DW RDNC100</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20133375</t>
+  </si>
+  <si>
+    <t>VSLNE LOT FLWLESS100</t>
+  </si>
+  <si>
+    <t>20142379</t>
+  </si>
+  <si>
+    <t>IDM KTK MKN POK SNRL</t>
+  </si>
+  <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20114021</t>
-  </si>
-  <si>
-    <t>IDM TISU WJH PRM 100</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20140679</t>
-  </si>
-  <si>
-    <t>IDM FC.TISSUE 3X80'S</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20035998</t>
-  </si>
-  <si>
-    <t>INDOMRET TRVL PACK50</t>
-  </si>
-  <si>
-    <t>20133704</t>
-  </si>
-  <si>
-    <t>IDM BB.FCL TISSU 70S</t>
-  </si>
-  <si>
-    <t>20000071</t>
-  </si>
-  <si>
-    <t>INDOMARET FAC.COTTON</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20003915</t>
-  </si>
-  <si>
-    <t>IDM ABON SAPI 100GR</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10029542</t>
-  </si>
-  <si>
-    <t>MR.BREAD COKLAT KEJU</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20087202</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 800</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20081452</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 800</t>
-  </si>
-  <si>
-    <t>20084152</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW MLD C800</t>
-  </si>
-  <si>
-    <t>20136390</t>
-  </si>
-  <si>
-    <t>VSLNE LOT DW RDNC100</t>
-  </si>
-  <si>
-    <t>20133375</t>
-  </si>
-  <si>
-    <t>VSLNE LOT FLWLESS100</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20140802</t>
-  </si>
-  <si>
-    <t>IDM TISU DAPUR 1+1</t>
-  </si>
-  <si>
-    <t>20139576</t>
-  </si>
-  <si>
-    <t>PC CRMY CPUCCINO 210</t>
-  </si>
-  <si>
-    <t>20139578</t>
-  </si>
-  <si>
-    <t>PC GOLDN CARAMEL 210</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
-  </si>
-  <si>
-    <t>20141597</t>
-  </si>
-  <si>
-    <t>FRUZZ GUMMY ASORTD36</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>20142397</t>
+  </si>
+  <si>
+    <t>IDM KTK MKN POK 3STA</t>
+  </si>
+  <si>
+    <t>20142393</t>
+  </si>
+  <si>
+    <t>IDM BTL MNM 6POKEMON</t>
+  </si>
+  <si>
+    <t>20142353</t>
+  </si>
+  <si>
+    <t>IDM BTL MNM PIKACHU</t>
+  </si>
+  <si>
+    <t>20142382</t>
+  </si>
+  <si>
+    <t>IDM KTK PNSL POK PIK</t>
   </si>
 </sst>
 </file>
@@ -568,14 +634,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -635,15 +701,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -652,78 +718,78 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -732,10 +798,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -749,133 +815,133 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -889,13 +955,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -909,13 +975,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -929,13 +995,13 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -949,13 +1015,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -969,33 +1035,213 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>29</v>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="82">
   <si>
     <t/>
   </si>
@@ -136,79 +136,94 @@
     <t>8</t>
   </si>
   <si>
-    <t>20016512</t>
-  </si>
-  <si>
-    <t>SUNCO MNYK GORENG 2L</t>
+    <t>20037131</t>
+  </si>
+  <si>
+    <t>PRIM-A AIR MNRAL 600</t>
+  </si>
+  <si>
+    <t>10003922</t>
+  </si>
+  <si>
+    <t>ABC KP&amp;GULA+SS.10X30</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20002725</t>
-  </si>
-  <si>
-    <t>KPL API SPC.MIX 20'S</t>
-  </si>
-  <si>
-    <t>20031318</t>
-  </si>
-  <si>
-    <t>G/DAY CPUCINO 10X25G</t>
-  </si>
-  <si>
-    <t>10002595</t>
-  </si>
-  <si>
-    <t>KRATINGDAENG 150 ML</t>
-  </si>
-  <si>
-    <t>20080924</t>
-  </si>
-  <si>
-    <t>YB BABY CRACK BNN 25</t>
+    <t>10026501</t>
+  </si>
+  <si>
+    <t>DK KACANG SUKRO 95G</t>
+  </si>
+  <si>
+    <t>20084707</t>
+  </si>
+  <si>
+    <t>SUKRO KC OVEN BWG 95</t>
+  </si>
+  <si>
+    <t>20062966</t>
+  </si>
+  <si>
+    <t>DK SUKRO BBQ 95G</t>
+  </si>
+  <si>
+    <t>10006195</t>
+  </si>
+  <si>
+    <t>SARI ROTI CKL-KEJU</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20010383</t>
+  </si>
+  <si>
+    <t>LIFEBUOY SHP A/D 340</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20136390</t>
+  </si>
+  <si>
+    <t>VSLNE LOT DW RDNC100</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20036752</t>
+  </si>
+  <si>
+    <t>C/LANG K/PTH ARMA 60</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20062974</t>
+  </si>
+  <si>
+    <t>C/LANG EKALPT LVN 60</t>
+  </si>
+  <si>
+    <t>10003163</t>
+  </si>
+  <si>
+    <t>ENZIM PG MINT 124G</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20141306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDM COSMETIC </t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20135430</t>
-  </si>
-  <si>
-    <t>LAURIER RN 18'S 35CM</t>
-  </si>
-  <si>
-    <t>20140679</t>
-  </si>
-  <si>
-    <t>IDM FC.TISSUE 3X80'S</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20136390</t>
-  </si>
-  <si>
-    <t>VSLNE LOT DW RDNC100</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20133375</t>
-  </si>
-  <si>
-    <t>VSLNE LOT FLWLESS100</t>
+    <t>20107245</t>
+  </si>
+  <si>
+    <t>PEPSODNT KDS PTRCK45</t>
   </si>
   <si>
     <t>20142379</t>
@@ -634,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -961,15 +976,15 @@
         <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -981,7 +996,7 @@
         <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1001,7 +1016,7 @@
         <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1041,35 +1056,35 @@
         <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1078,10 +1093,10 @@
         <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1118,7 +1133,7 @@
         <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>63</v>
@@ -1138,7 +1153,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>63</v>
@@ -1155,10 +1170,10 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>68</v>
@@ -1175,13 +1190,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1198,18 +1213,18 @@
         <v>17</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1218,18 +1233,18 @@
         <v>17</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1238,10 +1253,50 @@
         <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>68</v>
+      <c r="E31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
   <si>
     <t/>
   </si>
   <si>
-    <t>20036197</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 1 LT</t>
+    <t>20005529</t>
+  </si>
+  <si>
+    <t>NESTLE PURE LIFE 600</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -28,202 +28,190 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10004336</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN600</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20008767</t>
+  </si>
+  <si>
+    <t>CLUB AIR MNRAL 600ML</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20090527</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 600mL</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20065778</t>
+  </si>
+  <si>
+    <t>COCA COLA PET 390 ML</t>
+  </si>
+  <si>
     <t>RT,(E-14H)</t>
   </si>
   <si>
-    <t>20036200</t>
-  </si>
-  <si>
-    <t>SPRITE SOFT DRINK 1L</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20036199</t>
-  </si>
-  <si>
-    <t>FANTA STRAWBERRY 1 L</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20032503</t>
-  </si>
-  <si>
-    <t>MINUTE M. P/ORNGE 1L</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20005529</t>
-  </si>
-  <si>
-    <t>NESTLE PURE LIFE 600</t>
+    <t>20065780</t>
+  </si>
+  <si>
+    <t>FANTA STRW PET 390ML</t>
+  </si>
+  <si>
+    <t>20065779</t>
+  </si>
+  <si>
+    <t>SPRITE PET 390 ML</t>
+  </si>
+  <si>
+    <t>20060207</t>
+  </si>
+  <si>
+    <t>I/OCHA TEH MLATI 350</t>
+  </si>
+  <si>
+    <t>20048934</t>
+  </si>
+  <si>
+    <t>I/OCHA GRN TEA 350ML</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20090527</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 600mL</t>
+    <t>20118209</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT STRAW 250</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>10036647</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU UHT CHO1L</t>
-  </si>
-  <si>
-    <t>10004884</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CHO 950</t>
-  </si>
-  <si>
-    <t>10005909</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT PLN 950</t>
-  </si>
-  <si>
-    <t>20134390</t>
-  </si>
-  <si>
-    <t>CIMORY BBS LKTSA 250</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20138916</t>
-  </si>
-  <si>
-    <t>CIMORY THAI TEA 250</t>
-  </si>
-  <si>
-    <t>20104636</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOML 250</t>
-  </si>
-  <si>
-    <t>20112746</t>
-  </si>
-  <si>
-    <t>INDOMLK KIDS CKLT 6S</t>
+    <t>20130186</t>
+  </si>
+  <si>
+    <t>GRNFLD UHT CHOCO 250</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20112794</t>
-  </si>
-  <si>
-    <t>INDOMLK KIDS STRW 6S</t>
+    <t>10008887</t>
+  </si>
+  <si>
+    <t>ULTRA KCNG HIJAU 250</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>20037131</t>
-  </si>
-  <si>
-    <t>PRIM-A AIR MNRAL 600</t>
-  </si>
-  <si>
-    <t>10003922</t>
-  </si>
-  <si>
-    <t>ABC KP&amp;GULA+SS.10X30</t>
+    <t>10007385</t>
+  </si>
+  <si>
+    <t>ULTRA SR ASAM SLM250</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20016512</t>
+  </si>
+  <si>
+    <t>SUNCO MNYK GORENG 2L</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>10026501</t>
-  </si>
-  <si>
-    <t>DK KACANG SUKRO 95G</t>
-  </si>
-  <si>
-    <t>20084707</t>
-  </si>
-  <si>
-    <t>SUKRO KC OVEN BWG 95</t>
-  </si>
-  <si>
-    <t>20062966</t>
-  </si>
-  <si>
-    <t>DK SUKRO BBQ 95G</t>
-  </si>
-  <si>
-    <t>10006195</t>
-  </si>
-  <si>
-    <t>SARI ROTI CKL-KEJU</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20010383</t>
-  </si>
-  <si>
-    <t>LIFEBUOY SHP A/D 340</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20136390</t>
-  </si>
-  <si>
-    <t>VSLNE LOT DW RDNC100</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20036752</t>
-  </si>
-  <si>
-    <t>C/LANG K/PTH ARMA 60</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20062974</t>
-  </si>
-  <si>
-    <t>C/LANG EKALPT LVN 60</t>
-  </si>
-  <si>
-    <t>10003163</t>
-  </si>
-  <si>
-    <t>ENZIM PG MINT 124G</t>
+    <t>20109716</t>
+  </si>
+  <si>
+    <t>GLDNFL CHO CRNCH 350</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20107245</t>
-  </si>
-  <si>
-    <t>PEPSODNT KDS PTRCK45</t>
+    <t>20122061</t>
+  </si>
+  <si>
+    <t>OATSDE O/M B/BLND 1L</t>
+  </si>
+  <si>
+    <t>10006651</t>
+  </si>
+  <si>
+    <t>VAPE FMK ORANGE 600</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20124850</t>
+  </si>
+  <si>
+    <t>VAPE SPRY SWET PD600</t>
+  </si>
+  <si>
+    <t>20136134</t>
+  </si>
+  <si>
+    <t>VAPE CANDY FLO 600</t>
+  </si>
+  <si>
+    <t>20136130</t>
+  </si>
+  <si>
+    <t>VAPE FLO.BUBBLE 600</t>
+  </si>
+  <si>
+    <t>20098520</t>
+  </si>
+  <si>
+    <t>IDM TISSUE PNGST 150</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20134457</t>
+  </si>
+  <si>
+    <t>IN-LITE LED BOX 15W</t>
+  </si>
+  <si>
+    <t>20040313</t>
+  </si>
+  <si>
+    <t>MY BABY TELON PLUS30</t>
+  </si>
+  <si>
+    <t>20141306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDM COSMETIC </t>
   </si>
   <si>
     <t>20142379</t>
@@ -649,14 +637,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -716,15 +704,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -733,18 +721,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -753,7 +741,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -761,42 +749,42 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -813,10 +801,10 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -833,10 +821,10 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -853,18 +841,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -873,18 +861,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -893,18 +881,18 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -913,18 +901,18 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -933,290 +921,290 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1230,13 +1218,13 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1250,53 +1238,13 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,35 +11,104 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="70">
   <si>
     <t/>
   </si>
   <si>
+    <t>20139532</t>
+  </si>
+  <si>
+    <t>A/R BRS KHS PLN WG5</t>
+  </si>
+  <si>
+    <t>EG2A</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>10003974</t>
+  </si>
+  <si>
+    <t>TROPICAL MNYK BTL 2L</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20141306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDM COSMETIC </t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20033546</t>
+  </si>
+  <si>
+    <t>GRNFIELD CHOCO 950</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10001094</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 65G</t>
+  </si>
+  <si>
+    <t>20122264</t>
+  </si>
+  <si>
+    <t>CHITATO MI GORENG 65</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10001093</t>
+  </si>
+  <si>
+    <t>CHITATO AYAM BMB 65G</t>
+  </si>
+  <si>
+    <t>10015954</t>
+  </si>
+  <si>
+    <t>GAGA 100 JALAPENO 75</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
     <t>20005529</t>
   </si>
   <si>
     <t>NESTLE PURE LIFE 600</t>
   </si>
   <si>
-    <t>EG2A</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
     <t>10004336</t>
   </si>
   <si>
     <t>INDOMARET AIR MIN600</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>PT,(E-1H)</t>
   </si>
   <si>
@@ -49,30 +118,18 @@
     <t>CLUB AIR MNRAL 600ML</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
     <t>20090527</t>
   </si>
   <si>
     <t>CRYSTALIN BTL 600mL</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>20065778</t>
   </si>
   <si>
     <t>COCA COLA PET 390 ML</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
     <t>20065780</t>
   </si>
   <si>
@@ -97,9 +154,6 @@
     <t>I/OCHA GRN TEA 350ML</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>20118209</t>
   </si>
   <si>
@@ -134,84 +188,6 @@
   </si>
   <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>20016512</t>
-  </si>
-  <si>
-    <t>SUNCO MNYK GORENG 2L</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20109716</t>
-  </si>
-  <si>
-    <t>GLDNFL CHO CRNCH 350</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20122061</t>
-  </si>
-  <si>
-    <t>OATSDE O/M B/BLND 1L</t>
-  </si>
-  <si>
-    <t>10006651</t>
-  </si>
-  <si>
-    <t>VAPE FMK ORANGE 600</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20124850</t>
-  </si>
-  <si>
-    <t>VAPE SPRY SWET PD600</t>
-  </si>
-  <si>
-    <t>20136134</t>
-  </si>
-  <si>
-    <t>VAPE CANDY FLO 600</t>
-  </si>
-  <si>
-    <t>20136130</t>
-  </si>
-  <si>
-    <t>VAPE FLO.BUBBLE 600</t>
-  </si>
-  <si>
-    <t>20098520</t>
-  </si>
-  <si>
-    <t>IDM TISSUE PNGST 150</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20134457</t>
-  </si>
-  <si>
-    <t>IN-LITE LED BOX 15W</t>
-  </si>
-  <si>
-    <t>20040313</t>
-  </si>
-  <si>
-    <t>MY BABY TELON PLUS30</t>
-  </si>
-  <si>
-    <t>20141306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDM COSMETIC </t>
   </si>
   <si>
     <t>20142379</t>
@@ -637,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -738,13 +714,13 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -761,18 +737,18 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -781,10 +757,10 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -804,7 +780,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -821,70 +797,70 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -898,30 +874,30 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -929,10 +905,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -941,18 +917,18 @@
         <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -961,18 +937,18 @@
         <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -984,267 +960,207 @@
         <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="63">
   <si>
     <t/>
   </si>
   <si>
-    <t>20139532</t>
-  </si>
-  <si>
-    <t>A/R BRS KHS PLN WG5</t>
+    <t>20016512</t>
+  </si>
+  <si>
+    <t>SUNCO MNYK GORENG 2L</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -28,19 +28,97 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>10003974</t>
-  </si>
-  <si>
-    <t>TROPICAL MNYK BTL 2L</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20077483</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS26 XL</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10013205</t>
+  </si>
+  <si>
+    <t>SUNLIGHT J/NIPIS.750</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20138899</t>
+  </si>
+  <si>
+    <t>SNSLK SHP G.BLCK 160</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20115171</t>
+  </si>
+  <si>
+    <t>IDM TISU BAMBU 150'S</t>
+  </si>
+  <si>
+    <t>20055311</t>
+  </si>
+  <si>
+    <t>NABATI RCHSE WFR 110</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20055312</t>
+  </si>
+  <si>
+    <t>NBATI RCHCO WFR C110</t>
+  </si>
+  <si>
+    <t>10008867</t>
+  </si>
+  <si>
+    <t>SARI/R TAWAR GANDUM</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20089542</t>
+  </si>
+  <si>
+    <t>IDM AIR MN 8+ BTL500</t>
+  </si>
+  <si>
+    <t>RT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20140350</t>
+  </si>
+  <si>
+    <t>LARISST BMB MASAK 90</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20027167</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP400</t>
   </si>
   <si>
     <t>20141306</t>
@@ -49,154 +127,55 @@
     <t xml:space="preserve">IDM COSMETIC </t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20033546</t>
-  </si>
-  <si>
-    <t>GRNFIELD CHOCO 950</t>
+    <t>20003915</t>
+  </si>
+  <si>
+    <t>IDM ABON SAPI 100GR</t>
+  </si>
+  <si>
+    <t>20083529</t>
+  </si>
+  <si>
+    <t>HAPPY TOS SEAWEED 52</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10001094</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 65G</t>
-  </si>
-  <si>
-    <t>20122264</t>
-  </si>
-  <si>
-    <t>CHITATO MI GORENG 65</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10001093</t>
-  </si>
-  <si>
-    <t>CHITATO AYAM BMB 65G</t>
-  </si>
-  <si>
-    <t>10015954</t>
-  </si>
-  <si>
-    <t>GAGA 100 JALAPENO 75</t>
+    <t>20089255</t>
+  </si>
+  <si>
+    <t>IDM KCNG PNGGN 100G</t>
+  </si>
+  <si>
+    <t>20072370</t>
+  </si>
+  <si>
+    <t>IDM KCNG BUMBU 100G</t>
+  </si>
+  <si>
+    <t>20096682</t>
+  </si>
+  <si>
+    <t>IDM KACANG JUMBO 80</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20005529</t>
-  </si>
-  <si>
-    <t>NESTLE PURE LIFE 600</t>
-  </si>
-  <si>
-    <t>10004336</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN600</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20008767</t>
-  </si>
-  <si>
-    <t>CLUB AIR MNRAL 600ML</t>
-  </si>
-  <si>
-    <t>20090527</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 600mL</t>
-  </si>
-  <si>
-    <t>20065778</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 390 ML</t>
-  </si>
-  <si>
-    <t>20065780</t>
-  </si>
-  <si>
-    <t>FANTA STRW PET 390ML</t>
-  </si>
-  <si>
-    <t>20065779</t>
-  </si>
-  <si>
-    <t>SPRITE PET 390 ML</t>
-  </si>
-  <si>
-    <t>20060207</t>
-  </si>
-  <si>
-    <t>I/OCHA TEH MLATI 350</t>
-  </si>
-  <si>
-    <t>20048934</t>
-  </si>
-  <si>
-    <t>I/OCHA GRN TEA 350ML</t>
-  </si>
-  <si>
-    <t>20118209</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT STRAW 250</t>
+    <t>20139150</t>
+  </si>
+  <si>
+    <t>IDM KCNG KORO BLD 80</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20130186</t>
-  </si>
-  <si>
-    <t>GRNFLD UHT CHOCO 250</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10008887</t>
-  </si>
-  <si>
-    <t>ULTRA KCNG HIJAU 250</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>10007385</t>
-  </si>
-  <si>
-    <t>ULTRA SR ASAM SLM250</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>20142379</t>
   </si>
   <si>
     <t>IDM KTK MKN POK SNRL</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>20142397</t>
@@ -613,17 +592,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -642,8 +622,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -659,11 +645,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -679,11 +665,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -699,11 +685,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -714,21 +700,21 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H5" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -737,18 +723,18 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -757,18 +743,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -779,16 +765,16 @@
       <c r="E8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H8" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -797,13 +783,13 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -814,256 +800,256 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H10" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H14" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H15" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H22" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>59</v>
       </c>
@@ -1074,93 +1060,33 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="69">
   <si>
     <t/>
   </si>
   <si>
-    <t>20016512</t>
-  </si>
-  <si>
-    <t>SUNCO MNYK GORENG 2L</t>
+    <t>10003974</t>
+  </si>
+  <si>
+    <t>TROPICAL MNYK BTL 2L</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -31,70 +31,97 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20077483</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS26 XL</t>
+    <t>20103165</t>
+  </si>
+  <si>
+    <t>MERRIES PANT GS40 S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SUNLIGHT J/NIPIS.750</t>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20081452</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 800</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20084152</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW MLD C800</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20087202</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 800</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20037446</t>
+  </si>
+  <si>
+    <t>RNSO+ML LIQ ROSE 700</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20138899</t>
-  </si>
-  <si>
-    <t>SNSLK SHP G.BLCK 160</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20115171</t>
-  </si>
-  <si>
-    <t>IDM TISU BAMBU 150'S</t>
-  </si>
-  <si>
-    <t>20055311</t>
-  </si>
-  <si>
-    <t>NABATI RCHSE WFR 110</t>
+    <t>20131037</t>
+  </si>
+  <si>
+    <t>CHTATOLITE ABR.SWD65</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20023435</t>
+  </si>
+  <si>
+    <t>CHITATO SP BMB BKR65</t>
+  </si>
+  <si>
+    <t>20029228</t>
+  </si>
+  <si>
+    <t>CHITATO AYAM BBQ 65G</t>
+  </si>
+  <si>
+    <t>20133182</t>
+  </si>
+  <si>
+    <t>URAY NTURAL HONEY150</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20055312</t>
-  </si>
-  <si>
-    <t>NBATI RCHCO WFR C110</t>
-  </si>
-  <si>
-    <t>10008867</t>
-  </si>
-  <si>
-    <t>SARI/R TAWAR GANDUM</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
+    <t>20140350</t>
+  </si>
+  <si>
+    <t>LARISST BMB MASAK 90</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>20089542</t>
@@ -106,21 +133,18 @@
     <t>RT,(E-15H)</t>
   </si>
   <si>
-    <t>20140350</t>
-  </si>
-  <si>
-    <t>LARISST BMB MASAK 90</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
     <t>20027167</t>
   </si>
   <si>
     <t>IDM FAC.TISSUE NP400</t>
   </si>
   <si>
+    <t>20140679</t>
+  </si>
+  <si>
+    <t>IDM FC.TISSUE 3X80'S</t>
+  </si>
+  <si>
     <t>20141306</t>
   </si>
   <si>
@@ -160,16 +184,10 @@
     <t>IDM KACANG JUMBO 80</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>20139150</t>
   </si>
   <si>
     <t>IDM KCNG KORO BLD 80</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
   <si>
     <t>20142379</t>
@@ -592,18 +610,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,14 +639,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -645,11 +656,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -665,11 +676,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -685,11 +696,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -705,31 +716,31 @@
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -740,21 +751,21 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H7" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -763,18 +774,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -783,33 +794,33 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -820,16 +831,16 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -840,21 +851,21 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -863,78 +874,78 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F16" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -943,18 +954,18 @@
         <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -963,18 +974,18 @@
         <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -983,13 +994,13 @@
         <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -1000,16 +1011,16 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>55</v>
       </c>
@@ -1020,16 +1031,16 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>57</v>
       </c>
@@ -1040,16 +1051,16 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>59</v>
       </c>
@@ -1060,16 +1071,16 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>61</v>
       </c>
@@ -1080,13 +1091,73 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="82">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003974</t>
-  </si>
-  <si>
-    <t>TROPICAL MNYK BTL 2L</t>
+    <t>20112491</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 910</t>
   </si>
   <si>
     <t>EG2A</t>
@@ -28,166 +28,205 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20131788</t>
+  </si>
+  <si>
+    <t>MAMA LMN JR.NPS 950</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20028779</t>
+  </si>
+  <si>
+    <t>IDM KRBOL WNG650(BR)</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20089486</t>
+  </si>
+  <si>
+    <t>IDM KRBL SRH CTR 650</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20020226</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI PINK 765</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20080360</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 550ML</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20009500</t>
+  </si>
+  <si>
+    <t>BIORE B.FOAM RELX400</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20031215</t>
+  </si>
+  <si>
+    <t>BIORE BF LIVELY 400</t>
+  </si>
+  <si>
+    <t>20011007</t>
+  </si>
+  <si>
+    <t>LFBUOY BW M.CARE 380</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20011008</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 380</t>
+  </si>
+  <si>
+    <t>20112622</t>
+  </si>
+  <si>
+    <t>K.NAT BW COT.FLO 400</t>
+  </si>
+  <si>
+    <t>20120923</t>
+  </si>
+  <si>
+    <t>K.NAT BW SP.MGNO 400</t>
+  </si>
+  <si>
+    <t>20093101</t>
+  </si>
+  <si>
+    <t>ZEN BW A.BAC SHIS380</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20103165</t>
-  </si>
-  <si>
-    <t>MERRIES PANT GS40 S</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20081452</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 800</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20084152</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW MLD C800</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20087202</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 800</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20037446</t>
-  </si>
-  <si>
-    <t>RNSO+ML LIQ ROSE 700</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20131037</t>
-  </si>
-  <si>
-    <t>CHTATOLITE ABR.SWD65</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20023435</t>
-  </si>
-  <si>
-    <t>CHITATO SP BMB BKR65</t>
-  </si>
-  <si>
-    <t>20029228</t>
-  </si>
-  <si>
-    <t>CHITATO AYAM BBQ 65G</t>
-  </si>
-  <si>
-    <t>20133182</t>
-  </si>
-  <si>
-    <t>URAY NTURAL HONEY150</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20140350</t>
-  </si>
-  <si>
-    <t>LARISST BMB MASAK 90</t>
+    <t>20130709</t>
+  </si>
+  <si>
+    <t>LUX BW MGC ORCHD 825</t>
+  </si>
+  <si>
+    <t>20130710</t>
+  </si>
+  <si>
+    <t>LUX BW SKURA BLM 825</t>
+  </si>
+  <si>
+    <t>10013205</t>
+  </si>
+  <si>
+    <t>SUNLIGHT J/NIPIS.750</t>
+  </si>
+  <si>
+    <t>20139947</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 675G</t>
+  </si>
+  <si>
+    <t>20010383</t>
+  </si>
+  <si>
+    <t>LIFEBUOY SHP A/D 340</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20036752</t>
+  </si>
+  <si>
+    <t>C/LANG K/PTH ARMA 60</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20062974</t>
+  </si>
+  <si>
+    <t>C/LANG EKALPT LVN 60</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20016512</t>
+  </si>
+  <si>
+    <t>SUNCO MNYK GORENG 2L</t>
+  </si>
+  <si>
+    <t>20003915</t>
+  </si>
+  <si>
+    <t>IDM ABON SAPI 100GR</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20089542</t>
-  </si>
-  <si>
-    <t>IDM AIR MN 8+ BTL500</t>
-  </si>
-  <si>
-    <t>RT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20027167</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP400</t>
-  </si>
-  <si>
-    <t>20140679</t>
-  </si>
-  <si>
-    <t>IDM FC.TISSUE 3X80'S</t>
+    <t>20025825</t>
+  </si>
+  <si>
+    <t>PRONAS KORNETKU 200G</t>
+  </si>
+  <si>
+    <t>20055855</t>
+  </si>
+  <si>
+    <t>S/ROTI TWR DOUB.SOFT</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
   </si>
   <si>
     <t>20141306</t>
   </si>
   <si>
     <t xml:space="preserve">IDM COSMETIC </t>
-  </si>
-  <si>
-    <t>20003915</t>
-  </si>
-  <si>
-    <t>IDM ABON SAPI 100GR</t>
-  </si>
-  <si>
-    <t>20083529</t>
-  </si>
-  <si>
-    <t>HAPPY TOS SEAWEED 52</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20089255</t>
-  </si>
-  <si>
-    <t>IDM KCNG PNGGN 100G</t>
-  </si>
-  <si>
-    <t>20072370</t>
-  </si>
-  <si>
-    <t>IDM KCNG BUMBU 100G</t>
-  </si>
-  <si>
-    <t>20096682</t>
-  </si>
-  <si>
-    <t>IDM KACANG JUMBO 80</t>
-  </si>
-  <si>
-    <t>20139150</t>
-  </si>
-  <si>
-    <t>IDM KCNG KORO BLD 80</t>
   </si>
   <si>
     <t>20142379</t>
@@ -610,14 +649,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -737,7 +776,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -817,15 +856,15 @@
         <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -837,7 +876,7 @@
         <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -857,47 +896,47 @@
         <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -914,10 +953,10 @@
         <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -934,10 +973,10 @@
         <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -951,13 +990,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -971,33 +1010,33 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1011,41 +1050,41 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1054,98 +1093,98 @@
         <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1154,10 +1193,90 @@
         <v>19</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>36</v>
+      <c r="E28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="79">
   <si>
     <t/>
   </si>
@@ -34,7 +34,7 @@
     <t>20131788</t>
   </si>
   <si>
-    <t>MAMA LMN JR.NPS 950</t>
+    <t>MAMA LMN JR.NPS 920</t>
   </si>
   <si>
     <t>2</t>
@@ -139,100 +139,91 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20130709</t>
-  </si>
-  <si>
-    <t>LUX BW MGC ORCHD 825</t>
-  </si>
-  <si>
-    <t>20130710</t>
-  </si>
-  <si>
-    <t>LUX BW SKURA BLM 825</t>
-  </si>
-  <si>
-    <t>10013205</t>
-  </si>
-  <si>
-    <t>SUNLIGHT J/NIPIS.750</t>
-  </si>
-  <si>
-    <t>20139947</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 675G</t>
-  </si>
-  <si>
-    <t>20010383</t>
-  </si>
-  <si>
-    <t>LIFEBUOY SHP A/D 340</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20036752</t>
-  </si>
-  <si>
-    <t>C/LANG K/PTH ARMA 60</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20062974</t>
-  </si>
-  <si>
-    <t>C/LANG EKALPT LVN 60</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20016512</t>
-  </si>
-  <si>
-    <t>SUNCO MNYK GORENG 2L</t>
-  </si>
-  <si>
-    <t>20003915</t>
-  </si>
-  <si>
-    <t>IDM ABON SAPI 100GR</t>
+    <t>20138867</t>
+  </si>
+  <si>
+    <t>RNSO JAP PEACH 700G</t>
+  </si>
+  <si>
+    <t>PT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20141203</t>
+  </si>
+  <si>
+    <t>RINSO RYL GOLD 700G</t>
+  </si>
+  <si>
+    <t>20037446</t>
+  </si>
+  <si>
+    <t>RNSO+ML LIQ ROSE 700</t>
+  </si>
+  <si>
+    <t>20141369</t>
+  </si>
+  <si>
+    <t>RINSO P.BRZE BTL 650</t>
+  </si>
+  <si>
+    <t>20141373</t>
+  </si>
+  <si>
+    <t>RINSO PW.CLN BTL 650</t>
+  </si>
+  <si>
+    <t>20134060</t>
+  </si>
+  <si>
+    <t>GLAD2 CLNSR BLBRRY70</t>
+  </si>
+  <si>
+    <t>20141306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDM COSMETIC </t>
+  </si>
+  <si>
+    <t>10003974</t>
+  </si>
+  <si>
+    <t>TROPICAL MNYK BTL 2L</t>
+  </si>
+  <si>
+    <t>20065379</t>
+  </si>
+  <si>
+    <t>SGM SOYA1+ VANL 700G</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20070110</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU700</t>
+  </si>
+  <si>
+    <t>10011021</t>
+  </si>
+  <si>
+    <t>SIMBA CRL C/C COK 34</t>
+  </si>
+  <si>
+    <t>20117687</t>
+  </si>
+  <si>
+    <t>DLMNT BOBA MTCHA 240</t>
+  </si>
+  <si>
+    <t>20142379</t>
+  </si>
+  <si>
+    <t>IDM KTK MKN POK SNRL</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20025825</t>
-  </si>
-  <si>
-    <t>PRONAS KORNETKU 200G</t>
-  </si>
-  <si>
-    <t>20055855</t>
-  </si>
-  <si>
-    <t>S/ROTI TWR DOUB.SOFT</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20141306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDM COSMETIC </t>
-  </si>
-  <si>
-    <t>20142379</t>
-  </si>
-  <si>
-    <t>IDM KTK MKN POK SNRL</t>
   </si>
   <si>
     <t>20142397</t>
@@ -953,18 +944,18 @@
         <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -973,18 +964,18 @@
         <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -993,7 +984,7 @@
         <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1001,10 +992,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1013,7 +1004,7 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1021,10 +1012,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1033,10 +1024,10 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1053,18 +1044,18 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1073,18 +1064,18 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1101,10 +1092,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1116,15 +1107,15 @@
         <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1136,15 +1127,15 @@
         <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1156,15 +1147,15 @@
         <v>16</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1176,15 +1167,15 @@
         <v>19</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1196,15 +1187,15 @@
         <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1216,15 +1207,15 @@
         <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1236,15 +1227,15 @@
         <v>12</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1256,15 +1247,15 @@
         <v>16</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1276,7 +1267,7 @@
         <v>19</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/EG2A.xlsx
+++ b/EG2A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="72">
   <si>
     <t/>
   </si>
@@ -103,94 +103,130 @@
     <t>LARISST JELY MANG135</t>
   </si>
   <si>
-    <t>10033417</t>
-  </si>
-  <si>
-    <t>NTRILON 4 RYL VAN400</t>
-  </si>
-  <si>
-    <t>20016512</t>
-  </si>
-  <si>
-    <t>SUNCO MNYK GR 2 L</t>
+    <t>10006259</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO ENR 780G</t>
+  </si>
+  <si>
+    <t>20077508</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 600G</t>
+  </si>
+  <si>
+    <t>20074147</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 600</t>
+  </si>
+  <si>
+    <t>20141306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDM COSMETIC </t>
+  </si>
+  <si>
+    <t>10005838</t>
+  </si>
+  <si>
+    <t>FILMA MINYAK GR RF2L</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20117107</t>
-  </si>
-  <si>
-    <t>BANGO KECAP MNS 920G</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20042356</t>
-  </si>
-  <si>
-    <t>DIABETASOL SWET 50'S</t>
-  </si>
-  <si>
-    <t>20014537</t>
-  </si>
-  <si>
-    <t>BISKUAT ORIGNAL121.6</t>
-  </si>
-  <si>
-    <t>20141306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDM COSMETIC </t>
-  </si>
-  <si>
-    <t>20090918</t>
-  </si>
-  <si>
-    <t>SOFTEX PL D.SRH 20'S</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20081452</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 800</t>
+    <t>10005701</t>
+  </si>
+  <si>
+    <t>BOTAN PREMIUM 155GR</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10007970</t>
+  </si>
+  <si>
+    <t>BUAVITA JAMBU SL 245</t>
+  </si>
+  <si>
+    <t>10007974</t>
+  </si>
+  <si>
+    <t>BUAVITA LYCHEE SL245</t>
+  </si>
+  <si>
+    <t>10007972</t>
+  </si>
+  <si>
+    <t>BUAVITA JC APPLE 245</t>
+  </si>
+  <si>
+    <t>10007971</t>
+  </si>
+  <si>
+    <t>BUAVITA ORANGE SL245</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20138569</t>
+  </si>
+  <si>
+    <t>MOOOCHII CHOCO 40G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20138568</t>
+  </si>
+  <si>
+    <t>MOOOCHII RED BEAN40G</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10013205</t>
+  </si>
+  <si>
+    <t>SNLGHT J/NIPIS 675 G</t>
+  </si>
+  <si>
+    <t>20139948</t>
+  </si>
+  <si>
+    <t>SNLGHT BRY&amp;LME 675 G</t>
+  </si>
+  <si>
+    <t>20139947</t>
+  </si>
+  <si>
+    <t>SNLGHT B.BLBR 675 G</t>
+  </si>
+  <si>
+    <t>20110117</t>
+  </si>
+  <si>
+    <t>G&amp;L FC.FOAM VIT.C100</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20087202</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 800</t>
-  </si>
-  <si>
-    <t>20130709</t>
-  </si>
-  <si>
-    <t>LUX BW MGC ORCHD 825</t>
-  </si>
-  <si>
-    <t>20129580</t>
-  </si>
-  <si>
-    <t>GATSBY BALM CLAY 70</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20140874</t>
-  </si>
-  <si>
-    <t>G2G NIACND B.SRM 180</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>20067449</t>
+  </si>
+  <si>
+    <t>GLW&amp;LOVELY DRM.GL100</t>
+  </si>
+  <si>
+    <t>20142118</t>
+  </si>
+  <si>
+    <t>B/D STRNG POMADE 75</t>
   </si>
 </sst>
 </file>
@@ -583,14 +619,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -807,7 +843,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>16</v>
@@ -824,93 +860,93 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -924,112 +960,232 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="F22" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="E23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>20</v>
       </c>
     </row>
